--- a/artfynd/A 6412-2024 artfynd.xlsx
+++ b/artfynd/A 6412-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6412-2024 artfynd.xlsx
+++ b/artfynd/A 6412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112275735</v>
+        <v>47965</v>
       </c>
       <c r="B2" t="n">
-        <v>96761</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Farstalandet, Upl</t>
+          <t>söder om Beatelundsvägen fuktskog, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692677</v>
+        <v>692813</v>
       </c>
       <c r="R2" t="n">
-        <v>6577616</v>
+        <v>6577706</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två individer av vanlig groda observerades under svampplockningen. Söder om beatelundsvägen, i höjd med gräsmarken norr om vägen. Fuktig barrskog, mossa och fräken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,22 +778,123 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112275735</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Farstalandet, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>692676</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6577617</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ingarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Stella Malmgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Stella Malmgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
